--- a/Banque_et_assurance.xlsx
+++ b/Banque_et_assurance.xlsx
@@ -2271,7 +2271,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Gestion du risque bancaire</t>
+          <t>Gestion des risques bancaires</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
